--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131193769</v>
       </c>
       <c r="B2" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131193775</v>
       </c>
       <c r="B4" t="n">
-        <v>92467</v>
+        <v>92468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,40 +1012,36 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131203506</v>
+        <v>131203444</v>
       </c>
       <c r="B5" t="n">
-        <v>91870</v>
+        <v>92302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>5467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1054,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571386</v>
+        <v>571394</v>
       </c>
       <c r="R5" t="n">
-        <v>6446409</v>
+        <v>6446363</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,6 +1086,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,36 +1118,40 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131203444</v>
+        <v>131203506</v>
       </c>
       <c r="B6" t="n">
-        <v>92301</v>
+        <v>91871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5467</v>
+        <v>5321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1155,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571394</v>
+        <v>571386</v>
       </c>
       <c r="R6" t="n">
-        <v>6446363</v>
+        <v>6446409</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,11 +1196,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131193769</v>
       </c>
       <c r="B2" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>131193787</v>
       </c>
       <c r="B3" t="n">
-        <v>58041</v>
+        <v>58043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131193775</v>
       </c>
       <c r="B4" t="n">
-        <v>92468</v>
+        <v>92470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,36 +1012,40 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131203444</v>
+        <v>131203506</v>
       </c>
       <c r="B5" t="n">
-        <v>92302</v>
+        <v>91873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5467</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1050,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571394</v>
+        <v>571386</v>
       </c>
       <c r="R5" t="n">
-        <v>6446363</v>
+        <v>6446409</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,11 +1090,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,40 +1117,36 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131203506</v>
+        <v>131203444</v>
       </c>
       <c r="B6" t="n">
-        <v>91871</v>
+        <v>92304</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5321</v>
+        <v>5467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1160,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571386</v>
+        <v>571394</v>
       </c>
       <c r="R6" t="n">
-        <v>6446409</v>
+        <v>6446363</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1191,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131193769</v>
       </c>
       <c r="B2" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>131193787</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>58044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131193775</v>
       </c>
       <c r="B4" t="n">
-        <v>92470</v>
+        <v>92471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>131203506</v>
       </c>
       <c r="B5" t="n">
-        <v>91873</v>
+        <v>91874</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131203444</v>
       </c>
       <c r="B6" t="n">
-        <v>92304</v>
+        <v>92305</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131193769</v>
       </c>
       <c r="B2" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>131193787</v>
       </c>
       <c r="B3" t="n">
-        <v>58044</v>
+        <v>58045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131193775</v>
       </c>
       <c r="B4" t="n">
-        <v>92471</v>
+        <v>92472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>131203506</v>
       </c>
       <c r="B5" t="n">
-        <v>91874</v>
+        <v>91875</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131203444</v>
       </c>
       <c r="B6" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131193769</v>
       </c>
       <c r="B2" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>131193787</v>
       </c>
       <c r="B3" t="n">
-        <v>58045</v>
+        <v>58048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131193775</v>
       </c>
       <c r="B4" t="n">
-        <v>92472</v>
+        <v>92475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>131203506</v>
       </c>
       <c r="B5" t="n">
-        <v>91875</v>
+        <v>91878</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131203444</v>
       </c>
       <c r="B6" t="n">
-        <v>92306</v>
+        <v>92309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131193769</v>
       </c>
       <c r="B2" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>131193787</v>
       </c>
       <c r="B3" t="n">
-        <v>58048</v>
+        <v>58049</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131193775</v>
       </c>
       <c r="B4" t="n">
-        <v>92475</v>
+        <v>92476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>131203506</v>
       </c>
       <c r="B5" t="n">
-        <v>91878</v>
+        <v>91879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131203444</v>
       </c>
       <c r="B6" t="n">
-        <v>92309</v>
+        <v>92310</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131193769</v>
       </c>
       <c r="B2" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>131193787</v>
       </c>
       <c r="B3" t="n">
-        <v>58049</v>
+        <v>58055</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131193775</v>
       </c>
       <c r="B4" t="n">
-        <v>92476</v>
+        <v>92482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>131203506</v>
       </c>
       <c r="B5" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131203444</v>
       </c>
       <c r="B6" t="n">
-        <v>92310</v>
+        <v>92316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1221,6 +1221,698 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131928690</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97285</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>53</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Seboklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>571436</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6446286</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131926070</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91839</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Seboklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>571405</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6446340</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131939366</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 680, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>571394</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6446317</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Lena Lundin Johansson, Elsa Waldo, Emma Nordenberg, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131927063</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97285</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>53</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Seboklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>571384</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6446412</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131925911</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97285</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>53</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Seboklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>571405</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6446340</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131926929</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97285</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>53</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Seboklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>571399</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6446400</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131926357</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97285</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>53</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Seboklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>571353</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6446368</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1913,6 +1913,210 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131929006</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97285</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>53</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Seboklint, Seboklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>571404</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6446329</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elsa Waldo</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elsa Waldo, Emma Nordenberg, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131926413</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97285</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>53</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Seboklint, Seboklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>571408</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6446323</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elsa Waldo</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elsa Waldo, Emma Nordenberg, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>131928690</v>
       </c>
       <c r="B7" t="n">
-        <v>97285</v>
+        <v>97287</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>131926070</v>
       </c>
       <c r="B8" t="n">
-        <v>91839</v>
+        <v>91841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>131939366</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>131927063</v>
       </c>
       <c r="B10" t="n">
-        <v>97285</v>
+        <v>97287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>131925911</v>
       </c>
       <c r="B11" t="n">
-        <v>97285</v>
+        <v>97287</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>131926929</v>
       </c>
       <c r="B12" t="n">
-        <v>97285</v>
+        <v>97287</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>131926357</v>
       </c>
       <c r="B13" t="n">
-        <v>97285</v>
+        <v>97287</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>131929006</v>
       </c>
       <c r="B14" t="n">
-        <v>97285</v>
+        <v>97287</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>131926413</v>
       </c>
       <c r="B15" t="n">
-        <v>97285</v>
+        <v>97287</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>131928690</v>
       </c>
       <c r="B7" t="n">
-        <v>97287</v>
+        <v>97292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>131926070</v>
       </c>
       <c r="B8" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>131939366</v>
       </c>
       <c r="B9" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>131927063</v>
       </c>
       <c r="B10" t="n">
-        <v>97287</v>
+        <v>97292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>131925911</v>
       </c>
       <c r="B11" t="n">
-        <v>97287</v>
+        <v>97292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>131926929</v>
       </c>
       <c r="B12" t="n">
-        <v>97287</v>
+        <v>97292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>131926357</v>
       </c>
       <c r="B13" t="n">
-        <v>97287</v>
+        <v>97292</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>131929006</v>
       </c>
       <c r="B14" t="n">
-        <v>97287</v>
+        <v>97292</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>131926413</v>
       </c>
       <c r="B15" t="n">
-        <v>97287</v>
+        <v>97292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>131928690</v>
       </c>
       <c r="B7" t="n">
-        <v>97292</v>
+        <v>97294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>131926070</v>
       </c>
       <c r="B8" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Emma Nordenberg, Mats Oldenborg, Stefan Kasselstrand, Magnus Kasselstrand, Lena Lundin Johansson, Elsa Waldo</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1420,7 +1420,7 @@
         <v>131939366</v>
       </c>
       <c r="B9" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>131927063</v>
       </c>
       <c r="B10" t="n">
-        <v>97292</v>
+        <v>97294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>131925911</v>
       </c>
       <c r="B11" t="n">
-        <v>97292</v>
+        <v>97294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Emma Nordenberg, Mats Oldenborg, Stefan Kasselstrand, Magnus Kasselstrand, Lena Lundin Johansson, Elsa Waldo</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1724,7 +1724,7 @@
         <v>131926929</v>
       </c>
       <c r="B12" t="n">
-        <v>97292</v>
+        <v>97294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>131926357</v>
       </c>
       <c r="B13" t="n">
-        <v>97292</v>
+        <v>97294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>131929006</v>
       </c>
       <c r="B14" t="n">
-        <v>97292</v>
+        <v>97294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>131926413</v>
       </c>
       <c r="B15" t="n">
-        <v>97292</v>
+        <v>97294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Mats Oldenborg, Stefan Kasselstrand, Magnus Kasselstrand, Lena Lundin Johansson, Elsa Waldo</t>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Mats Oldenborg, Stefan Kasselstrand, Magnus Kasselstrand, Lena Lundin Johansson, Elsa Waldo</t>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>131928690</v>
       </c>
       <c r="B7" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>131926070</v>
       </c>
       <c r="B8" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>131927063</v>
       </c>
       <c r="B10" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>131925911</v>
       </c>
       <c r="B11" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Mats Oldenborg, Stefan Kasselstrand, Magnus Kasselstrand, Lena Lundin Johansson, Elsa Waldo</t>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1724,7 +1724,7 @@
         <v>131926929</v>
       </c>
       <c r="B12" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>131926357</v>
       </c>
       <c r="B13" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>131929006</v>
       </c>
       <c r="B14" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>131926413</v>
       </c>
       <c r="B15" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Lena Lundin Johansson, Elsa Waldo, Emma Nordenberg, Mats Oldenborg</t>
+          <t>Mats Oldenborg, Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>131928690</v>
       </c>
       <c r="B7" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>131926070</v>
       </c>
       <c r="B8" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>131939366</v>
       </c>
       <c r="B9" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mats Oldenborg, Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Lena Lundin Johansson, Elsa Waldo, Emma Nordenberg, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1530,7 +1530,7 @@
         <v>131927063</v>
       </c>
       <c r="B10" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Emma Nordenberg, Mats Oldenborg, Stefan Kasselstrand, Magnus Kasselstrand, Lena Lundin Johansson, Elsa Waldo</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1627,7 +1627,7 @@
         <v>131925911</v>
       </c>
       <c r="B11" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>131926929</v>
       </c>
       <c r="B12" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Emma Nordenberg, Mats Oldenborg, Stefan Kasselstrand, Magnus Kasselstrand, Lena Lundin Johansson, Elsa Waldo</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1821,7 +1821,7 @@
         <v>131926357</v>
       </c>
       <c r="B13" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>131929006</v>
       </c>
       <c r="B14" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>131926413</v>
       </c>
       <c r="B15" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elsa Waldo, Emma Nordenberg, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Elsa Waldo, Mats Oldenborg, Stefan Kasselstrand, Magnus Kasselstrand, Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2117,6 +2117,222 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132696536</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 680, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>571382</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6446406</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132698514</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101319</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 680, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>571409</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6446320</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>131928690</v>
       </c>
       <c r="B7" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>131926070</v>
       </c>
       <c r="B8" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>131939366</v>
       </c>
       <c r="B9" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>131927063</v>
       </c>
       <c r="B10" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Mats Oldenborg, Stefan Kasselstrand, Magnus Kasselstrand, Lena Lundin Johansson, Elsa Waldo</t>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1627,7 +1627,7 @@
         <v>131925911</v>
       </c>
       <c r="B11" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>131926929</v>
       </c>
       <c r="B12" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Mats Oldenborg, Stefan Kasselstrand, Magnus Kasselstrand, Lena Lundin Johansson, Elsa Waldo</t>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1821,7 +1821,7 @@
         <v>131926357</v>
       </c>
       <c r="B13" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>131929006</v>
       </c>
       <c r="B14" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>131926413</v>
       </c>
       <c r="B15" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elsa Waldo, Mats Oldenborg, Stefan Kasselstrand, Magnus Kasselstrand, Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Elsa Waldo, Emma Nordenberg, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2122,7 +2122,7 @@
         <v>132696536</v>
       </c>
       <c r="B16" t="n">
-        <v>99112</v>
+        <v>99116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>132698514</v>
       </c>
       <c r="B17" t="n">
-        <v>101319</v>
+        <v>101323</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -2122,7 +2122,7 @@
         <v>132696536</v>
       </c>
       <c r="B16" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>132698514</v>
       </c>
       <c r="B17" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>131929006</v>
       </c>
       <c r="B14" t="n">
-        <v>97356</v>
+        <v>97358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>131926413</v>
       </c>
       <c r="B15" t="n">
-        <v>97356</v>
+        <v>97358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>132696536</v>
       </c>
       <c r="B16" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>132698514</v>
       </c>
       <c r="B17" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -2232,7 +2232,7 @@
         <v>132698514</v>
       </c>
       <c r="B17" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -2122,7 +2122,7 @@
         <v>132696536</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>132698514</v>
       </c>
       <c r="B17" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -2122,7 +2122,7 @@
         <v>132696536</v>
       </c>
       <c r="B16" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>132698514</v>
       </c>
       <c r="B17" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -2122,7 +2122,7 @@
         <v>132696536</v>
       </c>
       <c r="B16" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>132698514</v>
       </c>
       <c r="B17" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131193769</v>
+        <v>131925911</v>
       </c>
       <c r="B2" t="n">
-        <v>91828</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,48 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 680, Falerum, Sm</t>
+          <t>Seboklint, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571404</v>
+        <v>571405</v>
       </c>
       <c r="R2" t="n">
-        <v>6446346</v>
+        <v>6446340</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Väldigt mkt på grov granlåga</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,29 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131193787</v>
+        <v>131926357</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,49 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 680, Falerum, Sm</t>
+          <t>Seboklint, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571404</v>
+        <v>571353</v>
       </c>
       <c r="R3" t="n">
-        <v>6446346</v>
+        <v>6446368</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,71 +857,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131193775</v>
+        <v>131926413</v>
       </c>
       <c r="B4" t="n">
-        <v>92482</v>
+        <v>97435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 680, Falerum, Sm</t>
+          <t>Seboklint, Seboklint, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571404</v>
+        <v>571408</v>
       </c>
       <c r="R4" t="n">
-        <v>6446346</v>
+        <v>6446323</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,17 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,64 +959,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Elsa Waldo</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Elsa Waldo, Emma Nordenberg, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131203506</v>
+        <v>131926929</v>
       </c>
       <c r="B5" t="n">
-        <v>91885</v>
+        <v>97435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 680, Falerum, Sm</t>
+          <t>Seboklint, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571386</v>
+        <v>571399</v>
       </c>
       <c r="R5" t="n">
-        <v>6446409</v>
+        <v>6446400</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,29 +1050,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131203444</v>
+        <v>131927063</v>
       </c>
       <c r="B6" t="n">
-        <v>92316</v>
+        <v>97435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,37 +1079,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5467</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 680, Falerum, Sm</t>
+          <t>Seboklint, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571394</v>
+        <v>571384</v>
       </c>
       <c r="R6" t="n">
-        <v>6446363</v>
+        <v>6446412</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,17 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,19 +1147,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1226,7 +1168,7 @@
         <v>131928690</v>
       </c>
       <c r="B7" t="n">
-        <v>97356</v>
+        <v>97435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131926070</v>
+        <v>131929006</v>
       </c>
       <c r="B8" t="n">
-        <v>91908</v>
+        <v>97435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,34 +1273,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Seboklint, Sm</t>
+          <t>Seboklint, Seboklint, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571405</v>
+        <v>571404</v>
       </c>
       <c r="R8" t="n">
-        <v>6446340</v>
+        <v>6446329</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,28 +1345,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Elsa Waldo</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Elsa Waldo, Emma Nordenberg, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131939366</v>
+        <v>131193769</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,31 +1375,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1460,10 +1410,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571394</v>
+        <v>571404</v>
       </c>
       <c r="R9" t="n">
-        <v>6446317</v>
+        <v>6446346</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1490,17 +1440,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spår efter födosök</t>
+          <t>Väldigt mkt på grov granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,6 +1459,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1520,17 +1471,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Lena Lundin Johansson, Elsa Waldo, Emma Nordenberg, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131927063</v>
+        <v>131926070</v>
       </c>
       <c r="B10" t="n">
-        <v>97356</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,21 +1489,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571384</v>
+        <v>571405</v>
       </c>
       <c r="R10" t="n">
-        <v>6446412</v>
+        <v>6446340</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,48 +1575,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131925911</v>
+        <v>131193775</v>
       </c>
       <c r="B11" t="n">
-        <v>97356</v>
+        <v>92564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Seboklint, Sm</t>
+          <t>A 680, Falerum, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571405</v>
+        <v>571404</v>
       </c>
       <c r="R11" t="n">
-        <v>6446340</v>
+        <v>6446346</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1689,12 +1651,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,63 +1670,71 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131926929</v>
+        <v>131203506</v>
       </c>
       <c r="B12" t="n">
-        <v>97356</v>
+        <v>91966</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>5321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Seboklint, Sm</t>
+          <t>A 680, Falerum, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571399</v>
+        <v>571386</v>
       </c>
       <c r="R12" t="n">
-        <v>6446400</v>
+        <v>6446409</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,12 +1761,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,28 +1775,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131926357</v>
+        <v>131203444</v>
       </c>
       <c r="B13" t="n">
-        <v>97356</v>
+        <v>92398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1829,34 +1805,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>5467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Seboklint, Sm</t>
+          <t>A 680, Falerum, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571353</v>
+        <v>571394</v>
       </c>
       <c r="R13" t="n">
-        <v>6446368</v>
+        <v>6446363</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,12 +1862,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,70 +1881,75 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131929006</v>
+        <v>131939366</v>
       </c>
       <c r="B14" t="n">
-        <v>97358</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Seboklint, Seboklint, Sm</t>
+          <t>A 680, Falerum, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571404</v>
+        <v>571394</v>
       </c>
       <c r="R14" t="n">
-        <v>6446329</v>
+        <v>6446317</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1992,35 +1981,39 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elsa Waldo</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elsa Waldo, Emma Nordenberg, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Lena Lundin Johansson, Elsa Waldo, Emma Nordenberg, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131926413</v>
+        <v>131193787</v>
       </c>
       <c r="B15" t="n">
-        <v>97358</v>
+        <v>58112</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,41 +2021,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>103020</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Seboklint, Seboklint, Sm</t>
+          <t>A 680, Falerum, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571408</v>
+        <v>571404</v>
       </c>
       <c r="R15" t="n">
-        <v>6446323</v>
+        <v>6446346</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2086,12 +2087,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2100,65 +2101,64 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elsa Waldo</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elsa Waldo, Emma Nordenberg, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132696536</v>
+        <v>132726601</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>58136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2166,13 +2166,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571382</v>
+        <v>571399</v>
       </c>
       <c r="R16" t="n">
-        <v>6446406</v>
+        <v>6446409</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2210,7 +2210,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2229,41 +2228,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132698514</v>
+        <v>132696536</v>
       </c>
       <c r="B17" t="n">
-        <v>101338</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2272,13 +2275,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571409</v>
+        <v>571382</v>
       </c>
       <c r="R17" t="n">
-        <v>6446320</v>
+        <v>6446406</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2328,10 +2331,116 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132698514</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 680, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>571409</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6446320</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 680-2026 artfynd.xlsx
+++ b/artfynd/A 680-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131925911</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926357</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926413</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926929</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131927063</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131928690</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131929006</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131193769</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1572,6 +1617,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926070</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1686,6 +1736,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131193775</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,6 +1846,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203506</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1897,6 +1957,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203444</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2007,6 +2072,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131939366</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131193787</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2225,6 +2300,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132726601</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2335,6 +2415,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132696536</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2441,8 +2526,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698514</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>